--- a/data/trans_orig/P33B_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R2-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>151764</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124780</t>
+          <t>131438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160419</t>
+          <t>171783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>289770</t>
+          <t>320393</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267610</t>
+          <t>297917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>309652</t>
+          <t>340909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>431316</t>
+          <t>472158</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403000</t>
+          <t>441880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>459713</t>
+          <t>503852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>373393</t>
+          <t>426765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354519</t>
+          <t>406746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390158</t>
+          <t>447091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>463398</t>
+          <t>500922</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>443516</t>
+          <t>480406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485558</t>
+          <t>523398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>836791</t>
+          <t>927687</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808394</t>
+          <t>895993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865107</t>
+          <t>957965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>240284</t>
+          <t>260060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165619</t>
+          <t>231704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282451</t>
+          <t>292163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>364897</t>
+          <t>413896</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273854</t>
+          <t>379124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>414961</t>
+          <t>445123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>605181</t>
+          <t>673956</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>486439</t>
+          <t>631227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680855</t>
+          <t>723194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2049013</t>
+          <t>1969425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2006846</t>
+          <t>1937322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2123678</t>
+          <t>1997781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1872926</t>
+          <t>1757496</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1822862</t>
+          <t>1726269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1963969</t>
+          <t>1792268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3921940</t>
+          <t>3726921</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3846266</t>
+          <t>3677683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4040682</t>
+          <t>3769650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>80897</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>100018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>104761</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78800</t>
+          <t>89627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108049</t>
+          <t>121054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>164467</t>
+          <t>185658</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142431</t>
+          <t>163675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187302</t>
+          <t>211104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>574657</t>
+          <t>630690</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557715</t>
+          <t>611569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>588649</t>
+          <t>647889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>567962</t>
+          <t>630116</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>552414</t>
+          <t>613823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581663</t>
+          <t>645250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1142619</t>
+          <t>1260806</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1119784</t>
+          <t>1235360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1164655</t>
+          <t>1282789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>350064</t>
+          <t>451731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>503136</t>
+          <t>535370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>747169</t>
+          <t>839051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>597175</t>
+          <t>796096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>811970</t>
+          <t>884285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1200964</t>
+          <t>1331771</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1046167</t>
+          <t>1273355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1301110</t>
+          <t>1399383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2997063</t>
+          <t>3026880</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2947723</t>
+          <t>2984231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3100795</t>
+          <t>3067870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2904286</t>
+          <t>2888534</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2839485</t>
+          <t>2843300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3054280</t>
+          <t>2931489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5901350</t>
+          <t>5915415</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5801204</t>
+          <t>5847803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6056147</t>
+          <t>5973831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
